--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
